--- a/step3-validation-test.xlsx
+++ b/step3-validation-test.xlsx
@@ -446,8 +446,8 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -525,7 +525,7 @@
           <t>はい/いいえ どちらも未選択</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
           <t>雇用者名/国/住所等の入力欄表示</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
@@ -589,7 +589,7 @@
           <t>雇用状況プルダウン表示</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -621,7 +621,7 @@
           <t>「(例) ABC CORPORATION」表示</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
@@ -653,7 +653,7 @@
           <t>60文字で止まる</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
@@ -685,7 +685,7 @@
           <t>許可される</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
@@ -717,7 +717,7 @@
           <t>「ABC CORPORATION」に変換</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
@@ -749,7 +749,7 @@
           <t>半角に変換</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
           <t>半角1つに</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
@@ -813,7 +813,7 @@
           <t>trimされる</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
@@ -845,7 +845,7 @@
           <t>「半角英数字で入力してください」表示</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
@@ -877,7 +877,7 @@
           <t>世界各国リストが表示</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
@@ -909,7 +909,7 @@
           <t>JAPAN(JPN)が絞り込み表示</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
@@ -941,7 +941,7 @@
           <t>除去される</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
@@ -973,7 +973,7 @@
           <t>「TOKYO」に変換</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1005,7 +1005,7 @@
           <t>許可される</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1037,7 +1037,7 @@
           <t>許可される</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1069,7 +1069,7 @@
           <t>除去される</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1101,7 +1101,7 @@
           <t>20桁で止まる</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1133,7 +1133,7 @@
           <t>「(例) ENGINEER」表示</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1165,7 +1165,7 @@
           <t>除去される</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1197,7 +1197,7 @@
           <t>「ENGINEER」に変換</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1229,7 +1229,7 @@
           <t>「選択してください」表示</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1261,7 +1261,7 @@
           <t>学生/無職/退職/主婦・主夫/子供/その他の6つ</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1293,7 +1293,7 @@
           <t>正常に選択される</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1325,7 +1325,7 @@
           <t>はい/いいえ未選択</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1357,7 +1357,7 @@
           <t>SNSプラットフォーム+アカウント名の入力欄表示</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1389,7 +1389,7 @@
           <t>入力欄非表示</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1421,7 +1421,7 @@
           <t>FB/Insta/X/LinkedIn/YT/TikTok/Weibo/その他</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1453,7 +1453,7 @@
           <t>「(例) @yamada_taro」表示</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1485,7 +1485,7 @@
           <t>正常に入力される</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
       <c r="H32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1517,7 +1517,7 @@
           <t>新しいSNS入力欄が追加される</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1549,7 +1549,7 @@
           <t>3つのSNSエントリが表示</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1581,7 +1581,7 @@
           <t>該当エントリが削除される</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1613,7 +1613,7 @@
           <t>「いいえ」選択</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1645,7 +1645,7 @@
           <t>姓/名/メール/電話の入力欄表示</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
@@ -1677,7 +1677,7 @@
           <t>除去される</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1709,7 +1709,7 @@
           <t>「YAMADA」に変換</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
@@ -1741,7 +1741,7 @@
           <t>40文字で止まる</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1773,7 +1773,7 @@
           <t>エラーメッセージ表示</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1805,7 +1805,7 @@
           <t>除去される</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
@@ -1837,7 +1837,7 @@
           <t>「HANAKO」に変換</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
@@ -1869,7 +1869,7 @@
           <t>エラーなし</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
       <c r="H44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
@@ -1901,7 +1901,7 @@
           <t>英字・ハイフン除去「090」</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1933,7 +1933,7 @@
           <t>20桁で止まる</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
@@ -1965,7 +1965,7 @@
           <t>「いいえ」選択</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
@@ -1997,7 +1997,7 @@
           <t>父/母の姓名入力欄表示</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
@@ -2029,7 +2029,7 @@
           <t>父の姓名入力欄が非表示</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
@@ -2061,7 +2061,7 @@
           <t>入力値がクリアされている</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2093,7 +2093,7 @@
           <t>除去される</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2125,7 +2125,7 @@
           <t>「YAMADA」に変換</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
       <c r="H52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2157,7 +2157,7 @@
           <t>40文字で止まる</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
       <c r="H53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2189,7 +2189,7 @@
           <t>除去される</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2221,7 +2221,7 @@
           <t>母の姓名入力欄が非表示</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2253,7 +2253,7 @@
           <t>「SUZUKI」に変換</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
       <c r="H56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2285,7 +2285,7 @@
           <t>「YOKO」に変換</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2317,7 +2317,7 @@
           <t>はい/いいえ どちらも未選択</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
       <c r="H58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
@@ -2349,7 +2349,7 @@
           <t>「はい」が選択状態になる</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2381,7 +2381,7 @@
           <t>「いいえ」が選択状態になる</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
       <c r="H60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2413,7 +2413,7 @@
           <t>全て正常に選択可能</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
@@ -2445,7 +2445,7 @@
           <t>正常に選択</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
       <c r="H62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2477,7 +2477,7 @@
           <t>進めない/エラー表示</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
@@ -2509,7 +2509,7 @@
           <t>⚠注意：すべて正直に…が表示</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
       <c r="H64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
@@ -2541,7 +2541,7 @@
           <t>スクロール可能なテキストが表示</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
@@ -2573,7 +2573,7 @@
           <t>全文が閲覧可能</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
       <c r="H66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
@@ -2605,7 +2605,7 @@
           <t>チェック状態になる</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
       <c r="H67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
@@ -2637,7 +2637,7 @@
           <t>スクロール可能なテキスト表示</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
       <c r="H68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
@@ -2669,7 +2669,7 @@
           <t>チェック状態になる</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
@@ -2701,7 +2701,7 @@
           <t>進めない/エラー表示</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
       <c r="H70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
@@ -2733,7 +2733,7 @@
           <t>進めない</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
@@ -2765,7 +2765,7 @@
           <t>正常に進む</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
       <c r="H72" s="4" t="inlineStr"/>
     </row>
   </sheetData>

--- a/step3-validation-test.xlsx
+++ b/step3-validation-test.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2768,6 +2768,114 @@
       <c r="G72" s="4" t="inlineStr"/>
       <c r="H72" s="4" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>苗字アラート</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先「はい」→姓に「SUZKI」入力→blur</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>⚠️アラート「もしかして SUZUKI ではありませんか？」が表示される</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>CSV仕様対応: attachSurnameAlert適用</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>父 姓</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>苗字アラート</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>両親「はい」→父の姓に「TNAKA」入力→blur</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>⚠️アラート「もしかして TANAKA ではありませんか？」が表示される</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>CSV仕様対応: attachSurnameAlert適用</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>母 姓</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>苗字アラート</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>母の姓に「SATOU」入力→blur</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>⚠️アラート「もしかして SATO ではありませんか？」が表示される</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>CSV仕様対応: attachSurnameAlert適用</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
